--- a/artfynd/A 15743-2024 artfynd.xlsx
+++ b/artfynd/A 15743-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74604733</v>
       </c>
       <c r="B2" t="n">
-        <v>95522</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97465</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>523830.8088811177</v>
+        <v>523831</v>
       </c>
       <c r="R2" t="n">
-        <v>6321245.066754761</v>
+        <v>6321245</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1984-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1990-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -804,12 +789,7 @@
         <v>74857349</v>
       </c>
       <c r="B3" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105642</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523830.8088811177</v>
+        <v>523831</v>
       </c>
       <c r="R3" t="n">
-        <v>6321245.066754761</v>
+        <v>6321245</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -874,19 +854,9 @@
           <t>1984-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1990-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 15743-2024 artfynd.xlsx
+++ b/artfynd/A 15743-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>74857349</v>
       </c>
       <c r="B3" t="n">
-        <v>105642</v>
+        <v>105651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15743-2024 artfynd.xlsx
+++ b/artfynd/A 15743-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74604733</v>
       </c>
       <c r="B2" t="n">
-        <v>97465</v>
+        <v>97466</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74857349</v>
       </c>
       <c r="B3" t="n">
-        <v>105651</v>
+        <v>105654</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15743-2024 artfynd.xlsx
+++ b/artfynd/A 15743-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74604733</v>
       </c>
       <c r="B2" t="n">
-        <v>97466</v>
+        <v>97493</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74857349</v>
       </c>
       <c r="B3" t="n">
-        <v>105654</v>
+        <v>105682</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15743-2024 artfynd.xlsx
+++ b/artfynd/A 15743-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74604733</v>
       </c>
       <c r="B2" t="n">
-        <v>97493</v>
+        <v>97499</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74857349</v>
       </c>
       <c r="B3" t="n">
-        <v>105682</v>
+        <v>105688</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15743-2024 artfynd.xlsx
+++ b/artfynd/A 15743-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74604733</v>
       </c>
       <c r="B2" t="n">
-        <v>97499</v>
+        <v>97506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74857349</v>
       </c>
       <c r="B3" t="n">
-        <v>105688</v>
+        <v>105695</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15743-2024 artfynd.xlsx
+++ b/artfynd/A 15743-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74604733</v>
       </c>
       <c r="B2" t="n">
-        <v>97506</v>
+        <v>97510</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74857349</v>
       </c>
       <c r="B3" t="n">
-        <v>105695</v>
+        <v>105699</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15743-2024 artfynd.xlsx
+++ b/artfynd/A 15743-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74604733</v>
       </c>
       <c r="B2" t="n">
-        <v>97510</v>
+        <v>97517</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74857349</v>
       </c>
       <c r="B3" t="n">
-        <v>105699</v>
+        <v>105706</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15743-2024 artfynd.xlsx
+++ b/artfynd/A 15743-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74604733</v>
       </c>
       <c r="B2" t="n">
-        <v>97520</v>
+        <v>97525</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74857349</v>
       </c>
       <c r="B3" t="n">
-        <v>105709</v>
+        <v>105714</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15743-2024 artfynd.xlsx
+++ b/artfynd/A 15743-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74604733</v>
       </c>
       <c r="B2" t="n">
-        <v>97525</v>
+        <v>97533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74857349</v>
       </c>
       <c r="B3" t="n">
-        <v>105714</v>
+        <v>105722</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15743-2024 artfynd.xlsx
+++ b/artfynd/A 15743-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74604733</v>
       </c>
       <c r="B2" t="n">
-        <v>97533</v>
+        <v>97543</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74857349</v>
       </c>
       <c r="B3" t="n">
-        <v>105722</v>
+        <v>105732</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15743-2024 artfynd.xlsx
+++ b/artfynd/A 15743-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74604733</v>
+        <v>74857349</v>
       </c>
       <c r="B2" t="n">
-        <v>97543</v>
+        <v>106243</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 5F4e 3149. SOM: Lycopodium clavatum. LEG: Yvonne Jakobsson, Alva Gustafsson, Kerstin Petersson</t>
+          <t>Smålands flora 2007: KOO: 5F4e 3149. SOM: Pyrola chlorantha. LEG: Yvonne Jakobsson, Alva Gustafsson, Kerstin Petersson</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74857349</v>
+        <v>74604733</v>
       </c>
       <c r="B3" t="n">
-        <v>105732</v>
+        <v>97986</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>221946</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -861,7 +861,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 5F4e 3149. SOM: Pyrola chlorantha. LEG: Yvonne Jakobsson, Alva Gustafsson, Kerstin Petersson</t>
+          <t>Smålands flora 2007: KOO: 5F4e 3149. SOM: Lycopodium clavatum. LEG: Yvonne Jakobsson, Alva Gustafsson, Kerstin Petersson</t>
         </is>
       </c>
       <c r="AD3" t="b">
